--- a/DOM/AFOLU/A2_Structure_Lists.xlsx
+++ b/DOM/AFOLU/A2_Structure_Lists.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="499">
   <si>
     <t>Year</t>
   </si>
@@ -109,7 +109,7 @@
     <t>PPPVD</t>
   </si>
   <si>
-    <t>PPPVDS</t>
+    <t>PPDHYD</t>
   </si>
   <si>
     <t>SOIALL</t>
@@ -226,6 +226,18 @@
     <t>IMP_STOR</t>
   </si>
   <si>
+    <t>CAMFOR</t>
+  </si>
+  <si>
+    <t>CAMCUL</t>
+  </si>
+  <si>
+    <t>CAMPAS</t>
+  </si>
+  <si>
+    <t>CAMASENTA</t>
+  </si>
+  <si>
     <t>REF_DSL</t>
   </si>
   <si>
@@ -265,6 +277,36 @@
     <t>PPICEGASFOI</t>
   </si>
   <si>
+    <t>PPADSL</t>
+  </si>
+  <si>
+    <t>PPAFOI</t>
+  </si>
+  <si>
+    <t>PPANGS</t>
+  </si>
+  <si>
+    <t>PPDBIM</t>
+  </si>
+  <si>
+    <t>PPDBGS</t>
+  </si>
+  <si>
+    <t>PPDDSL</t>
+  </si>
+  <si>
+    <t>PPDFOI</t>
+  </si>
+  <si>
+    <t>PPDNGS</t>
+  </si>
+  <si>
+    <t>PPDGSL</t>
+  </si>
+  <si>
+    <t>PPDGLP</t>
+  </si>
+  <si>
     <t>ELE_TRANS</t>
   </si>
   <si>
@@ -907,9 +949,6 @@
     <t>E1COA</t>
   </si>
   <si>
-    <t>E1IEL</t>
-  </si>
-  <si>
     <t>E1ELE</t>
   </si>
   <si>
@@ -988,6 +1027,18 @@
     <t>CLK_PROD</t>
   </si>
   <si>
+    <t>E5CAMFOR</t>
+  </si>
+  <si>
+    <t>E5CAMCUL</t>
+  </si>
+  <si>
+    <t>E5CAMPAS</t>
+  </si>
+  <si>
+    <t>E5CAMASENTA</t>
+  </si>
+  <si>
     <t>E2ELE</t>
   </si>
   <si>
@@ -1396,64 +1447,67 @@
     <t>E6TRNOMOT</t>
   </si>
   <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>CO2e_WASTE</t>
+  </si>
+  <si>
+    <t>CO2e_AP</t>
+  </si>
+  <si>
+    <t>contam_agua</t>
+  </si>
+  <si>
+    <t>CO2e_HFC</t>
+  </si>
+  <si>
+    <t>CO2e_PP</t>
+  </si>
+  <si>
+    <t>CONHAB</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>CONTUR</t>
+  </si>
+  <si>
+    <t>CONVAR</t>
+  </si>
+  <si>
+    <t>RESHID</t>
+  </si>
+  <si>
+    <t>CO2e_TRN</t>
+  </si>
+  <si>
+    <t>salud_residuos</t>
+  </si>
+  <si>
+    <t>CO2e_sources</t>
+  </si>
+  <si>
+    <t>CO2e_DE</t>
+  </si>
+  <si>
+    <t>DAPANI</t>
+  </si>
+  <si>
     <t>turismo_residuos</t>
   </si>
   <si>
-    <t>RESHID</t>
+    <t>CO2e_PIUP</t>
+  </si>
+  <si>
+    <t>CO2e_AFOLU</t>
   </si>
   <si>
     <t>FERT_ORG</t>
   </si>
   <si>
-    <t>contam_agua</t>
-  </si>
-  <si>
-    <t>CO2e_TRN</t>
-  </si>
-  <si>
     <t>CONHICK</t>
-  </si>
-  <si>
-    <t>CONHAB</t>
-  </si>
-  <si>
-    <t>CONVAR</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>CO2e_WASTE</t>
-  </si>
-  <si>
-    <t>CO2e_HFC</t>
-  </si>
-  <si>
-    <t>CO2e_DE</t>
-  </si>
-  <si>
-    <t>DAPANI</t>
-  </si>
-  <si>
-    <t>CO2e_AFOLU</t>
-  </si>
-  <si>
-    <t>CO2e_sources</t>
-  </si>
-  <si>
-    <t>RM</t>
-  </si>
-  <si>
-    <t>CONTUR</t>
-  </si>
-  <si>
-    <t>CO2e_PP</t>
-  </si>
-  <si>
-    <t>salud_residuos</t>
-  </si>
-  <si>
-    <t>CO2e_PIUP</t>
   </si>
   <si>
     <t>RD</t>
@@ -1814,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1848,19 +1902,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1871,10 +1925,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="E3" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1885,10 +1939,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1899,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1913,10 +1967,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E6" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1927,10 +1981,10 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1941,10 +1995,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E8" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1955,10 +2009,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="E9" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1969,10 +2023,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E10" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1983,10 +2037,10 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E11" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1997,10 +2051,10 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2011,10 +2065,10 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="E13" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2025,10 +2079,10 @@
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E14" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2039,10 +2093,10 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="E15" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2053,10 +2107,10 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E16" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2067,10 +2121,10 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="E17" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2081,10 +2135,10 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E18" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2095,10 +2149,10 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E19" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2109,10 +2163,10 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="E20" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2123,10 +2177,10 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E21" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2137,7 +2191,10 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>303</v>
+        <v>317</v>
+      </c>
+      <c r="E22" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2148,7 +2205,7 @@
         <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2159,7 +2216,7 @@
         <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2170,7 +2227,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2181,7 +2238,7 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2192,7 +2249,7 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2203,7 +2260,7 @@
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2214,7 +2271,7 @@
         <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2225,7 +2282,7 @@
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2236,7 +2293,7 @@
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2247,7 +2304,7 @@
         <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2258,7 +2315,7 @@
         <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2269,7 +2326,7 @@
         <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2277,7 +2334,7 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2285,7 +2342,7 @@
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2293,7 +2350,7 @@
         <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>318</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2301,7 +2358,7 @@
         <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2309,7 +2366,7 @@
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2317,7 +2374,7 @@
         <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2325,7 +2382,7 @@
         <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2333,7 +2390,7 @@
         <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2341,7 +2398,7 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>322</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2349,7 +2406,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2357,7 +2414,7 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2365,7 +2422,7 @@
         <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2373,7 +2430,7 @@
         <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2381,7 +2438,7 @@
         <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="2:4">
@@ -2389,7 +2446,7 @@
         <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="2:4">
@@ -2397,7 +2454,7 @@
         <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="2:4">
@@ -2405,7 +2462,7 @@
         <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="2:4">
@@ -2413,7 +2470,7 @@
         <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -2421,7 +2478,7 @@
         <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="2:4">
@@ -2429,7 +2486,7 @@
         <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -2437,7 +2494,7 @@
         <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="2:4">
@@ -2445,7 +2502,7 @@
         <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="2:4">
@@ -2453,7 +2510,7 @@
         <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="2:4">
@@ -2461,7 +2518,7 @@
         <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59" spans="2:4">
@@ -2469,7 +2526,7 @@
         <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="2:4">
@@ -2477,7 +2534,7 @@
         <v>65</v>
       </c>
       <c r="D60" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" spans="2:4">
@@ -2485,7 +2542,7 @@
         <v>66</v>
       </c>
       <c r="D61" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" spans="2:4">
@@ -2493,7 +2550,7 @@
         <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="2:4">
@@ -2501,7 +2558,7 @@
         <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -2509,7 +2566,7 @@
         <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -2517,7 +2574,7 @@
         <v>70</v>
       </c>
       <c r="D65" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" spans="2:4">
@@ -2525,7 +2582,7 @@
         <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="67" spans="2:4">
@@ -2533,7 +2590,7 @@
         <v>72</v>
       </c>
       <c r="D67" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="2:4">
@@ -2541,7 +2598,7 @@
         <v>73</v>
       </c>
       <c r="D68" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" spans="2:4">
@@ -2549,7 +2606,7 @@
         <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="70" spans="2:4">
@@ -2557,7 +2614,7 @@
         <v>75</v>
       </c>
       <c r="D70" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -2565,7 +2622,7 @@
         <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -2573,7 +2630,7 @@
         <v>77</v>
       </c>
       <c r="D72" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
     </row>
     <row r="73" spans="2:4">
@@ -2581,7 +2638,7 @@
         <v>78</v>
       </c>
       <c r="D73" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -2589,7 +2646,7 @@
         <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
     </row>
     <row r="75" spans="2:4">
@@ -2597,7 +2654,7 @@
         <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -2605,7 +2662,7 @@
         <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="2:4">
@@ -2613,7 +2670,7 @@
         <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="78" spans="2:4">
@@ -2621,7 +2678,7 @@
         <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79" spans="2:4">
@@ -2629,7 +2686,7 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80" spans="2:4">
@@ -2637,7 +2694,7 @@
         <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="81" spans="2:4">
@@ -2645,7 +2702,7 @@
         <v>86</v>
       </c>
       <c r="D81" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="82" spans="2:4">
@@ -2653,7 +2710,7 @@
         <v>87</v>
       </c>
       <c r="D82" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="2:4">
@@ -2661,7 +2718,7 @@
         <v>88</v>
       </c>
       <c r="D83" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="84" spans="2:4">
@@ -2669,7 +2726,7 @@
         <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
     </row>
     <row r="85" spans="2:4">
@@ -2677,7 +2734,7 @@
         <v>90</v>
       </c>
       <c r="D85" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="2:4">
@@ -2685,7 +2742,7 @@
         <v>91</v>
       </c>
       <c r="D86" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="2:4">
@@ -2693,7 +2750,7 @@
         <v>92</v>
       </c>
       <c r="D87" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="88" spans="2:4">
@@ -2701,7 +2758,7 @@
         <v>93</v>
       </c>
       <c r="D88" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="89" spans="2:4">
@@ -2709,7 +2766,7 @@
         <v>94</v>
       </c>
       <c r="D89" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="90" spans="2:4">
@@ -2717,7 +2774,7 @@
         <v>95</v>
       </c>
       <c r="D90" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
     </row>
     <row r="91" spans="2:4">
@@ -2725,7 +2782,7 @@
         <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="2:4">
@@ -2733,7 +2790,7 @@
         <v>97</v>
       </c>
       <c r="D92" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" spans="2:4">
@@ -2741,7 +2798,7 @@
         <v>98</v>
       </c>
       <c r="D93" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
     </row>
     <row r="94" spans="2:4">
@@ -2749,7 +2806,7 @@
         <v>99</v>
       </c>
       <c r="D94" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" spans="2:4">
@@ -2757,7 +2814,7 @@
         <v>100</v>
       </c>
       <c r="D95" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
     </row>
     <row r="96" spans="2:4">
@@ -2765,7 +2822,7 @@
         <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
     </row>
     <row r="97" spans="2:4">
@@ -2773,7 +2830,7 @@
         <v>102</v>
       </c>
       <c r="D97" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" spans="2:4">
@@ -2781,7 +2838,7 @@
         <v>103</v>
       </c>
       <c r="D98" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
     <row r="99" spans="2:4">
@@ -2789,7 +2846,7 @@
         <v>104</v>
       </c>
       <c r="D99" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="100" spans="2:4">
@@ -2797,7 +2854,7 @@
         <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="101" spans="2:4">
@@ -2805,7 +2862,7 @@
         <v>106</v>
       </c>
       <c r="D101" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
     </row>
     <row r="102" spans="2:4">
@@ -2813,7 +2870,7 @@
         <v>107</v>
       </c>
       <c r="D102" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="103" spans="2:4">
@@ -2821,7 +2878,7 @@
         <v>108</v>
       </c>
       <c r="D103" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
     </row>
     <row r="104" spans="2:4">
@@ -2829,7 +2886,7 @@
         <v>109</v>
       </c>
       <c r="D104" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
     </row>
     <row r="105" spans="2:4">
@@ -2837,7 +2894,7 @@
         <v>110</v>
       </c>
       <c r="D105" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
     </row>
     <row r="106" spans="2:4">
@@ -2845,7 +2902,7 @@
         <v>111</v>
       </c>
       <c r="D106" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="107" spans="2:4">
@@ -2853,7 +2910,7 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
     </row>
     <row r="108" spans="2:4">
@@ -2861,7 +2918,7 @@
         <v>113</v>
       </c>
       <c r="D108" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="2:4">
@@ -2869,7 +2926,7 @@
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
     </row>
     <row r="110" spans="2:4">
@@ -2877,7 +2934,7 @@
         <v>115</v>
       </c>
       <c r="D110" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
     </row>
     <row r="111" spans="2:4">
@@ -2885,7 +2942,7 @@
         <v>116</v>
       </c>
       <c r="D111" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
     </row>
     <row r="112" spans="2:4">
@@ -2893,7 +2950,7 @@
         <v>117</v>
       </c>
       <c r="D112" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
     </row>
     <row r="113" spans="2:4">
@@ -2901,7 +2958,7 @@
         <v>118</v>
       </c>
       <c r="D113" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
     </row>
     <row r="114" spans="2:4">
@@ -2909,7 +2966,7 @@
         <v>119</v>
       </c>
       <c r="D114" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115" spans="2:4">
@@ -2917,7 +2974,7 @@
         <v>120</v>
       </c>
       <c r="D115" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
     </row>
     <row r="116" spans="2:4">
@@ -2925,7 +2982,7 @@
         <v>121</v>
       </c>
       <c r="D116" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="117" spans="2:4">
@@ -2933,7 +2990,7 @@
         <v>122</v>
       </c>
       <c r="D117" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" spans="2:4">
@@ -2941,7 +2998,7 @@
         <v>123</v>
       </c>
       <c r="D118" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="119" spans="2:4">
@@ -2949,7 +3006,7 @@
         <v>124</v>
       </c>
       <c r="D119" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
     </row>
     <row r="120" spans="2:4">
@@ -2957,7 +3014,7 @@
         <v>125</v>
       </c>
       <c r="D120" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
     </row>
     <row r="121" spans="2:4">
@@ -2965,7 +3022,7 @@
         <v>126</v>
       </c>
       <c r="D121" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="122" spans="2:4">
@@ -2973,7 +3030,7 @@
         <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
     </row>
     <row r="123" spans="2:4">
@@ -2981,7 +3038,7 @@
         <v>128</v>
       </c>
       <c r="D123" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
     </row>
     <row r="124" spans="2:4">
@@ -2989,7 +3046,7 @@
         <v>129</v>
       </c>
       <c r="D124" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
     </row>
     <row r="125" spans="2:4">
@@ -2997,7 +3054,7 @@
         <v>130</v>
       </c>
       <c r="D125" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
     </row>
     <row r="126" spans="2:4">
@@ -3005,7 +3062,7 @@
         <v>131</v>
       </c>
       <c r="D126" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
     </row>
     <row r="127" spans="2:4">
@@ -3013,7 +3070,7 @@
         <v>132</v>
       </c>
       <c r="D127" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
     </row>
     <row r="128" spans="2:4">
@@ -3021,7 +3078,7 @@
         <v>133</v>
       </c>
       <c r="D128" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
     </row>
     <row r="129" spans="2:4">
@@ -3029,7 +3086,7 @@
         <v>134</v>
       </c>
       <c r="D129" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="2:4">
@@ -3037,7 +3094,7 @@
         <v>135</v>
       </c>
       <c r="D130" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
     </row>
     <row r="131" spans="2:4">
@@ -3045,7 +3102,7 @@
         <v>136</v>
       </c>
       <c r="D131" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -3053,7 +3110,7 @@
         <v>137</v>
       </c>
       <c r="D132" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -3061,7 +3118,7 @@
         <v>138</v>
       </c>
       <c r="D133" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
     </row>
     <row r="134" spans="2:4">
@@ -3069,7 +3126,7 @@
         <v>139</v>
       </c>
       <c r="D134" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="135" spans="2:4">
@@ -3077,7 +3134,7 @@
         <v>140</v>
       </c>
       <c r="D135" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -3085,7 +3142,7 @@
         <v>141</v>
       </c>
       <c r="D136" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -3093,7 +3150,7 @@
         <v>142</v>
       </c>
       <c r="D137" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -3101,7 +3158,7 @@
         <v>143</v>
       </c>
       <c r="D138" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -3109,7 +3166,7 @@
         <v>144</v>
       </c>
       <c r="D139" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="140" spans="2:4">
@@ -3117,7 +3174,7 @@
         <v>145</v>
       </c>
       <c r="D140" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="141" spans="2:4">
@@ -3125,7 +3182,7 @@
         <v>146</v>
       </c>
       <c r="D141" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -3133,7 +3190,7 @@
         <v>147</v>
       </c>
       <c r="D142" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -3141,7 +3198,7 @@
         <v>148</v>
       </c>
       <c r="D143" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -3149,7 +3206,7 @@
         <v>149</v>
       </c>
       <c r="D144" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
     </row>
     <row r="145" spans="2:4">
@@ -3157,7 +3214,7 @@
         <v>150</v>
       </c>
       <c r="D145" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
     </row>
     <row r="146" spans="2:4">
@@ -3165,7 +3222,7 @@
         <v>151</v>
       </c>
       <c r="D146" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -3173,7 +3230,7 @@
         <v>152</v>
       </c>
       <c r="D147" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -3181,7 +3238,7 @@
         <v>153</v>
       </c>
       <c r="D148" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -3189,7 +3246,7 @@
         <v>154</v>
       </c>
       <c r="D149" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -3197,7 +3254,7 @@
         <v>155</v>
       </c>
       <c r="D150" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -3205,7 +3262,7 @@
         <v>156</v>
       </c>
       <c r="D151" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -3213,7 +3270,7 @@
         <v>157</v>
       </c>
       <c r="D152" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -3221,7 +3278,7 @@
         <v>158</v>
       </c>
       <c r="D153" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
     </row>
     <row r="154" spans="2:4">
@@ -3229,7 +3286,7 @@
         <v>159</v>
       </c>
       <c r="D154" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -3237,7 +3294,7 @@
         <v>160</v>
       </c>
       <c r="D155" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -3245,7 +3302,7 @@
         <v>161</v>
       </c>
       <c r="D156" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -3253,7 +3310,7 @@
         <v>162</v>
       </c>
       <c r="D157" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="158" spans="2:4">
@@ -3261,7 +3318,7 @@
         <v>163</v>
       </c>
       <c r="D158" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -3269,7 +3326,7 @@
         <v>164</v>
       </c>
       <c r="D159" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -3277,7 +3334,7 @@
         <v>165</v>
       </c>
       <c r="D160" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -3285,7 +3342,7 @@
         <v>166</v>
       </c>
       <c r="D161" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
     </row>
     <row r="162" spans="2:4">
@@ -3293,7 +3350,7 @@
         <v>167</v>
       </c>
       <c r="D162" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -3301,7 +3358,7 @@
         <v>168</v>
       </c>
       <c r="D163" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -3309,7 +3366,7 @@
         <v>169</v>
       </c>
       <c r="D164" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -3317,7 +3374,7 @@
         <v>170</v>
       </c>
       <c r="D165" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
     </row>
     <row r="166" spans="2:4">
@@ -3325,7 +3382,7 @@
         <v>171</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
     </row>
     <row r="167" spans="2:4">
@@ -3333,7 +3390,7 @@
         <v>172</v>
       </c>
       <c r="D167" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
     </row>
     <row r="168" spans="2:4">
@@ -3341,7 +3398,7 @@
         <v>173</v>
       </c>
       <c r="D168" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -3349,7 +3406,7 @@
         <v>174</v>
       </c>
       <c r="D169" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="170" spans="2:4">
@@ -3357,7 +3414,7 @@
         <v>175</v>
       </c>
       <c r="D170" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -3365,7 +3422,7 @@
         <v>176</v>
       </c>
       <c r="D171" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -3373,7 +3430,7 @@
         <v>177</v>
       </c>
       <c r="D172" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -3381,7 +3438,7 @@
         <v>178</v>
       </c>
       <c r="D173" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="174" spans="2:4">
@@ -3389,7 +3446,7 @@
         <v>179</v>
       </c>
       <c r="D174" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
     </row>
     <row r="175" spans="2:4">
@@ -3397,7 +3454,7 @@
         <v>180</v>
       </c>
       <c r="D175" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
     </row>
     <row r="176" spans="2:4">
@@ -3405,7 +3462,7 @@
         <v>181</v>
       </c>
       <c r="D176" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
     </row>
     <row r="177" spans="2:4">
@@ -3413,7 +3470,7 @@
         <v>182</v>
       </c>
       <c r="D177" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="178" spans="2:4">
@@ -3421,7 +3478,7 @@
         <v>183</v>
       </c>
       <c r="D178" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
     </row>
     <row r="179" spans="2:4">
@@ -3429,7 +3486,7 @@
         <v>184</v>
       </c>
       <c r="D179" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="180" spans="2:4">
@@ -3437,7 +3494,7 @@
         <v>185</v>
       </c>
       <c r="D180" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
     </row>
     <row r="181" spans="2:4">
@@ -3445,7 +3502,7 @@
         <v>186</v>
       </c>
       <c r="D181" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="182" spans="2:4">
@@ -3453,23 +3510,32 @@
         <v>187</v>
       </c>
       <c r="D182" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
     </row>
     <row r="183" spans="2:4">
       <c r="B183" t="s">
         <v>188</v>
       </c>
+      <c r="D183" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="184" spans="2:4">
       <c r="B184" t="s">
         <v>189</v>
       </c>
+      <c r="D184" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="185" spans="2:4">
       <c r="B185" t="s">
         <v>190</v>
       </c>
+      <c r="D185" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="186" spans="2:4">
       <c r="B186" t="s">
@@ -3926,255 +3992,77 @@
         <v>281</v>
       </c>
     </row>
+    <row r="277" spans="2:2">
+      <c r="B277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBEC2896-298B-480E-92D3-AE97FD25A4E9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61ECCC5B-F852-4669-AC24-FAB280A8D679}"/>
 </file>